--- a/Result/profitability/5508.xlsx
+++ b/Result/profitability/5508.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,25 +669,25 @@
         <v>2.37</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5825</v>
+        <v>1.07625</v>
       </c>
       <c r="N2" t="n">
-        <v>44.2925</v>
+        <v>42.9075</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,16 +780,16 @@
         <v>3.39</v>
       </c>
       <c r="M3" t="n">
-        <v>1.38875</v>
+        <v>1.3225</v>
       </c>
       <c r="N3" t="n">
-        <v>43.075</v>
+        <v>41.70375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.68</v>
       </c>
       <c r="M4" t="n">
-        <v>1.42125</v>
+        <v>1.36375</v>
       </c>
       <c r="N4" t="n">
-        <v>42.16875</v>
+        <v>41.05875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>1.26125</v>
+        <v>1.3225</v>
       </c>
       <c r="N5" t="n">
-        <v>37.58875</v>
+        <v>36.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.67</v>
       </c>
       <c r="M6" t="n">
-        <v>1.295</v>
+        <v>1.34375</v>
       </c>
       <c r="N6" t="n">
-        <v>35.03625</v>
+        <v>34.245</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1.3575</v>
+        <v>1.3675</v>
       </c>
       <c r="N7" t="n">
-        <v>33.20875</v>
+        <v>32.6675</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3825</v>
+        <v>1.385</v>
       </c>
       <c r="N8" t="n">
-        <v>31.79125</v>
+        <v>31.1425</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>0.74</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7825</v>
+        <v>0.7825000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>25.31125</v>
@@ -1899,7 +1899,7 @@
         <v>0.48</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6325000000000001</v>
+        <v>0.6325</v>
       </c>
       <c r="N12" t="n">
         <v>23.51125</v>
@@ -2026,7 +2026,7 @@
         <v>1.14</v>
       </c>
       <c r="M13" t="n">
-        <v>0.76625</v>
+        <v>0.7662500000000001</v>
       </c>
       <c r="N13" t="n">
         <v>25.89625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5508</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>991</v>
+      </c>
+      <c r="D75" t="n">
+        <v>623</v>
+      </c>
+      <c r="E75" t="n">
+        <v>368</v>
+      </c>
+      <c r="F75" t="n">
+        <v>37.12</v>
+      </c>
+      <c r="G75" t="n">
+        <v>265</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>26.79%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-25</v>
+      </c>
+      <c r="J75" t="n">
+        <v>241</v>
+      </c>
+      <c r="K75" t="n">
+        <v>193</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.3975</v>
+      </c>
+      <c r="N75" t="n">
+        <v>43.95625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.02298850574712641</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.190000000000005</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1226660363980148</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-7.910000000000004</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1756606706640018</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
